--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104607_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104607_W17.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4687</v>
+        <v>5.9046</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9693</v>
+        <v>2.3378</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4994</v>
+        <v>3.5668</v>
       </c>
       <c r="G2" t="n">
-        <v>4.714</v>
+        <v>4.6991</v>
       </c>
       <c r="H2" t="n">
-        <v>1.726</v>
+        <v>1.7125</v>
       </c>
       <c r="I2" t="n">
-        <v>2.988</v>
+        <v>2.9866</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0357</v>
+        <v>3.9958</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2472</v>
+        <v>2.2161</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7885</v>
+        <v>1.7797</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6784</v>
+        <v>0.7033</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1909</v>
+        <v>0.2848</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9043</v>
+        <v>-0.4601</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7134</v>
+        <v>0.7449</v>
       </c>
       <c r="V2" t="n">
-        <v>3.2138</v>
+        <v>3.197</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3746</v>
+        <v>3.3547</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1263</v>
+        <v>2.6531</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0025</v>
+        <v>2.1731</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1238</v>
+        <v>0.48</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4795</v>
+        <v>3.4771</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3134</v>
+        <v>-0.2967</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7929</v>
+        <v>3.7738</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5974</v>
+        <v>4.5659</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8701</v>
+        <v>3.842</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1179</v>
+        <v>-1.0888</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1905</v>
+        <v>0.3322</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3266</v>
+        <v>-0.1165</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1361</v>
+        <v>0.4487</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0727</v>
+        <v>2.4925</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1251</v>
+        <v>0.3533</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1978</v>
+        <v>2.1392</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4513</v>
+        <v>1.4509</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2221</v>
+        <v>1.2262</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2292</v>
+        <v>0.2247</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7643</v>
+        <v>2.7384</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2397</v>
+        <v>1.2271</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5246</v>
+        <v>1.5114</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.313</v>
+        <v>-1.2876</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007</v>
+        <v>0.4286</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3962</v>
+        <v>0.1204</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4031</v>
+        <v>0.3082</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6962</v>
+        <v>0.9305</v>
       </c>
       <c r="E5" t="n">
-        <v>1.894</v>
+        <v>-1.2824</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1978</v>
+        <v>2.2129</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6163999999999999</v>
+        <v>1.0154</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0114</v>
+        <v>0.887</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6051</v>
+        <v>0.1284</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3317</v>
+        <v>0.9701</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1775</v>
+        <v>0.6722</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1541</v>
+        <v>0.2979</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7152</v>
+        <v>0.0452</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1662</v>
+        <v>0.2148</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.549</v>
+        <v>-0.1695</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4407</v>
+        <v>0.4403</v>
       </c>
       <c r="T5" t="n">
-        <v>0.738</v>
+        <v>0.253</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7027</v>
+        <v>0.1873</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>-0.2292</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8568</v>
+        <v>0.8868</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4891</v>
+        <v>3.3593</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6323</v>
+        <v>-2.4724</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6921</v>
+        <v>1.6896</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4216</v>
+        <v>-0.4085</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1136</v>
+        <v>2.0982</v>
       </c>
       <c r="J6" t="n">
-        <v>3.895</v>
+        <v>3.8695</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9772</v>
+        <v>2.9559</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2029</v>
+        <v>-2.1799</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1893</v>
+        <v>0.2184</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0212</v>
+        <v>-0.0746</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1681</v>
+        <v>0.2929</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7988</v>
+        <v>0.7075</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.359</v>
+        <v>0.1949</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1578</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0013</v>
+        <v>0.1173</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8786</v>
+        <v>-0.3103</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1227</v>
+        <v>0.4276</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9739</v>
+        <v>0.1462</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6754</v>
+        <v>0.0345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2985</v>
+        <v>0.1117</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0274</v>
+        <v>-0.0289</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2033</v>
+        <v>-0.3447</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1759</v>
+        <v>0.3159</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3173</v>
+        <v>0.2927</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1603</v>
+        <v>0.0487</v>
       </c>
       <c r="U7" t="n">
-        <v>0.157</v>
+        <v>0.244</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3856</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6442</v>
+        <v>0.4624</v>
       </c>
       <c r="E8" t="n">
-        <v>0.077</v>
+        <v>1.2548</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5672</v>
+        <v>-0.7924</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1148</v>
+        <v>0.6271</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3117</v>
+        <v>0.0224</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4265</v>
+        <v>0.6048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1466</v>
+        <v>2.3188</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>1.1721</v>
       </c>
       <c r="L8" t="n">
-        <v>0.112</v>
+        <v>1.1467</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0318</v>
+        <v>-1.6916</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3463</v>
+        <v>-1.1497</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3145</v>
+        <v>-0.5419</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2365</v>
+        <v>1.201</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>0.1228</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3061</v>
+        <v>1.0782</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GASPA</t>
+          <t>P. PAULICAP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,19 +1111,19 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2268</v>
+        <v>0.2621</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.0907</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2268</v>
+        <v>0.3528</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.1724</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0.1724</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1138,46 +1138,46 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.1724</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.1724</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.0907</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.0907</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. PAULICAP</t>
+          <t>M. GASPA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,19 +1189,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1379</v>
+        <v>0.2276</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2087</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3466</v>
+        <v>0.2276</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1732</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1732</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1216,40 +1216,40 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1732</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1732</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2087</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4291</v>
+        <v>-0.2905</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0046</v>
+        <v>-2.0873</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5754</v>
+        <v>1.7968</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2687</v>
+        <v>0.2457</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5784</v>
+        <v>-1.5905</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8471</v>
+        <v>1.8362</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4512</v>
+        <v>0.403</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.884</v>
+        <v>-0.9145</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3353</v>
+        <v>1.3175</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1825</v>
+        <v>-0.1573</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6944</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3702</v>
+        <v>0.532</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1875</v>
+        <v>-0.214</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5577</v>
+        <v>0.746</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7395</v>
+        <v>-4.4832</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.014</v>
+        <v>-2.7818</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7255</v>
+        <v>-1.7014</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0722</v>
+        <v>-5.0754</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1991</v>
+        <v>-1.1977</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.873</v>
+        <v>-3.8777</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9706</v>
+        <v>-1.9941</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5754</v>
+        <v>-1.587</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1016</v>
+        <v>-3.0813</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.2976</v>
+        <v>-2.2907</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1059</v>
+        <v>0.3646</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0907</v>
+        <v>0.3505</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0151</v>
+        <v>0.0141</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2074</v>
+        <v>-5.3759</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5215</v>
+        <v>-1.8092</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.6859</v>
+        <v>-3.5667</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5066</v>
+        <v>-2.5094</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8109</v>
+        <v>-1.8122</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6957</v>
+        <v>-0.6972</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7613</v>
+        <v>-0.7754</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2437</v>
+        <v>-1.2518</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7453</v>
+        <v>-1.734</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8084</v>
+        <v>0.015</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6261</v>
+        <v>0.1043</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1824</v>
+        <v>-0.0893</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.652400000000002</v>
+        <v>4.377500000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1990000000000007</v>
+        <v>1.621800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4533</v>
+        <v>2.755800000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5861</v>
+        <v>5.565</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.9702</v>
+        <v>-1.9402</v>
       </c>
       <c r="I14" t="n">
-        <v>7.556399999999998</v>
+        <v>7.5054</v>
       </c>
       <c r="J14" t="n">
-        <v>16.4639</v>
+        <v>16.2382</v>
       </c>
       <c r="K14" t="n">
-        <v>4.496599999999999</v>
+        <v>4.385999999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>11.9673</v>
+        <v>11.8522</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.8776</v>
+        <v>-10.6733</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.466699999999999</v>
+        <v>-6.3262</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.411</v>
+        <v>-4.3467</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.4024</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.2808</v>
+        <v>-19.3487</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8782</v>
+        <v>15.9342</v>
       </c>
       <c r="S14" t="n">
-        <v>2.268400000000001</v>
+        <v>4.018899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7088</v>
+        <v>0.04380000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9769</v>
+        <v>3.975</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7998</v>
+        <v>-1.7919</v>
       </c>
       <c r="W14" t="n">
-        <v>4.7246</v>
+        <v>4.6883</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.5242</v>
+        <v>-6.4803</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1421</v>
+        <v>3.5945</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9741</v>
+        <v>2.6458</v>
       </c>
       <c r="F15" t="n">
-        <v>1.168</v>
+        <v>0.9487</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2524</v>
+        <v>2.2513</v>
       </c>
       <c r="H15" t="n">
-        <v>2.231</v>
+        <v>2.218</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7177</v>
+        <v>3.6955</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9714</v>
+        <v>2.9508</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4653</v>
+        <v>-1.4442</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2072</v>
+        <v>0.6619</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6816</v>
+        <v>0.3875</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5256</v>
+        <v>0.2744</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4746</v>
+        <v>2.1873</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3721</v>
+        <v>3.8601</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8976</v>
+        <v>-1.6728</v>
       </c>
       <c r="G16" t="n">
-        <v>3.318</v>
+        <v>3.3117</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3522</v>
+        <v>4.3376</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0342</v>
+        <v>-1.026</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3028</v>
+        <v>5.273</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6684</v>
+        <v>4.64</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9848</v>
+        <v>-1.9613</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2044</v>
+        <v>-0.4901</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1179</v>
+        <v>-0.5903</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.1002</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8282</v>
+        <v>0.9862</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2888</v>
+        <v>0.4021</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5394</v>
+        <v>0.584</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6864</v>
+        <v>0.6945</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9076</v>
+        <v>0.9103</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2212</v>
+        <v>-0.2158</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4063</v>
+        <v>0.4047</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2944</v>
+        <v>0.293</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>0.28</v>
+        <v>0.2898</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6132</v>
+        <v>0.6173</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5387</v>
+        <v>-0.3913</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2604</v>
+        <v>-0.2309</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6081</v>
+        <v>0.6242</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7658</v>
+        <v>-1.5477</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3739</v>
+        <v>2.1719</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2573</v>
+        <v>0.2628</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1053</v>
+        <v>0.1062</v>
       </c>
       <c r="I18" t="n">
-        <v>0.152</v>
+        <v>0.1566</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0337</v>
+        <v>-0.0402</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>0.291</v>
+        <v>0.303</v>
       </c>
       <c r="N18" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0614</v>
+        <v>-0.0452</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4951</v>
+        <v>0.2755</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1573</v>
+        <v>0.3959</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-0.5633</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1573</v>
+        <v>0.9593</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1573</v>
+        <v>-4.4819</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1573</v>
+        <v>-1.8099</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-2.6721</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-1.9614</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.5311</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.4303</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1573</v>
+        <v>-2.5205</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>-1.2788</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.2417</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.9592</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.1868</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.2603</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.5532</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2929</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.22</v>
+        <v>0.1579</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0168</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7968</v>
+        <v>0.1579</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.4971</v>
+        <v>0.1579</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8183</v>
+        <v>0.1579</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6788</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9501</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5266</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4234</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.547</v>
+        <v>0.1579</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2917</v>
+        <v>0.1579</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2554</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9488</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1757</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8571</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0253</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1681</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9679</v>
+        <v>-0.8678</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9127</v>
+        <v>-1.1492</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9448</v>
+        <v>0.2814</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0956</v>
+        <v>-0.8401</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5757</v>
+        <v>1.2066</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5198</v>
+        <v>-2.0467</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0463</v>
+        <v>1.0634</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7029</v>
+        <v>1.4511</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3434</v>
+        <v>-0.3877</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9507</v>
+        <v>-1.9036</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1272</v>
+        <v>-0.2446</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8236</v>
+        <v>-1.659</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0415</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6293</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1388</v>
+        <v>-0.1871</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3297</v>
+        <v>-0.4811</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4685</v>
+        <v>0.294</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1607</v>
+        <v>0.387</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2481</v>
+        <v>-1.128</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4705</v>
+        <v>-1.8204</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2224</v>
+        <v>0.6924</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.835</v>
+        <v>1.1049</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2122</v>
+        <v>0.5772</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0471</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0862</v>
+        <v>2.0333</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4648</v>
+        <v>0.6927</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3786</v>
+        <v>1.3405</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9212</v>
+        <v>-0.9284</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2526</v>
+        <v>-0.1155</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6685</v>
+        <v>-0.8129</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5719</v>
+        <v>-0.0264</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8347</v>
+        <v>-0.2115</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2628</v>
+        <v>0.1851</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3856</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7445</v>
+        <v>-1.562</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7406</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0039</v>
+        <v>-0.6492</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4513</v>
+        <v>-1.4509</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.593</v>
+        <v>-0.5944</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8583</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3774</v>
+        <v>2.3459</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0767</v>
+        <v>1.058</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3007</v>
+        <v>1.288</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.8287</v>
+        <v>-3.7968</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6698</v>
+        <v>-1.6524</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6412</v>
+        <v>-0.4462</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.744</v>
+        <v>-0.8623</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1028</v>
+        <v>0.416</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0285</v>
+        <v>1.018</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0285</v>
+        <v>1.018</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0168</v>
+        <v>-1.7544</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9202</v>
+        <v>-0.8192</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0966</v>
+        <v>-0.9352</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1614</v>
+        <v>-2.1506</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3015</v>
+        <v>0.307</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.4629</v>
+        <v>-2.4576</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1766</v>
+        <v>-0.1893</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2468</v>
+        <v>1.2411</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9848</v>
+        <v>-1.9613</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7361</v>
+        <v>-0.4947</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6775</v>
+        <v>-0.5601</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0587</v>
+        <v>0.0653</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.5832</v>
+        <v>-2.4567</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3761</v>
+        <v>-1.1947</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2072</v>
+        <v>-1.2621</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4446</v>
+        <v>-1.4629</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.8915</v>
+        <v>-3.9026</v>
       </c>
       <c r="I25" t="n">
-        <v>2.4469</v>
+        <v>2.4397</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3607</v>
+        <v>-0.407</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.7484</v>
+        <v>-3.7726</v>
       </c>
       <c r="L25" t="n">
-        <v>3.3877</v>
+        <v>3.3655</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0839</v>
+        <v>-1.0558</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9408</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6584</v>
+        <v>-0.519</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.747</v>
+        <v>-0.5113</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0886</v>
+        <v>-0.0077</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="26">
@@ -2437,58 +2437,58 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.0821</v>
+        <v>-2.812</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.8859</v>
+        <v>-1.6564</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1963</v>
+        <v>-1.1556</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.9639</v>
+        <v>-2.9617</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5699</v>
+        <v>-1.5737</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.4258</v>
+        <v>-1.4169</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3451</v>
+        <v>-0.0779</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3478</v>
+        <v>-0.1116</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0027</v>
+        <v>0.0338</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.6523</v>
+        <v>-2.6349</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.453600000000001</v>
+        <v>-2.755699999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1990000000000001</v>
+        <v>0.1206999999999998</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.5863</v>
+        <v>-5.565</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9701</v>
+        <v>1.940199999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-7.5564</v>
+        <v>-7.5054</v>
       </c>
       <c r="J27" t="n">
-        <v>10.8775</v>
+        <v>10.6731</v>
       </c>
       <c r="K27" t="n">
-        <v>6.466700000000001</v>
+        <v>6.326299999999998</v>
       </c>
       <c r="L27" t="n">
-        <v>4.411099999999999</v>
+        <v>4.3468</v>
       </c>
       <c r="M27" t="n">
-        <v>-16.4639</v>
+        <v>-16.2381</v>
       </c>
       <c r="N27" t="n">
-        <v>-4.4966</v>
+        <v>-4.386</v>
       </c>
       <c r="O27" t="n">
-        <v>-11.9673</v>
+        <v>-11.8523</v>
       </c>
       <c r="P27" t="n">
-        <v>3.4024</v>
+        <v>3.4144</v>
       </c>
       <c r="Q27" t="n">
-        <v>-15.8782</v>
+        <v>-15.9342</v>
       </c>
       <c r="R27" t="n">
-        <v>19.2807</v>
+        <v>19.3486</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.977</v>
+        <v>-3.975</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7086</v>
+        <v>1.6986</v>
       </c>
       <c r="V27" t="n">
-        <v>1.7996</v>
+        <v>1.7919</v>
       </c>
       <c r="W27" t="n">
-        <v>6.524100000000001</v>
+        <v>6.4803</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.7244</v>
+        <v>-4.6885</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104607_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104607_W17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.4803</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104607_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-4.6885</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
